--- a/data/trending_integrated_20261022_15.xlsx
+++ b/data/trending_integrated_20261022_15.xlsx
@@ -567,24 +567,24 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3660</v>
+        <v>3675</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+18.45%</t>
+          <t>'+18.93%</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>352</v>
+        <v>365</v>
       </c>
       <c r="F2" t="n">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="G2" t="n">
-        <v>828</v>
+        <v>924</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -610,7 +610,7 @@
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>87954624834</v>
+        <v>88757121995</v>
       </c>
       <c r="P2" t="n">
         <v>7050</v>
@@ -626,16 +626,16 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>김정은 신변 이상설로 인한 급등세, 단기 변동성 및 향후 전망에 대한 분석.</t>
+          <t>김정은 위원장 신변 이상설 및 사망설 관련 급등 기대감. 과거 사례 기반 단기 급등 후 폭락 가능성 언급. 전쟁 가능성 대두.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['김정은', '신변이상설', '급등']</t>
+          <t>['신변 이상설', '사망설', '급등 기대']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>55200</v>
+        <v>55000</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+15.72%</t>
+          <t>'+15.30%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>0.02</v>
       </c>
       <c r="E3" t="n">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="F3" t="n">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="G3" t="n">
-        <v>1509</v>
+        <v>1536</v>
       </c>
       <c r="H3" t="n">
         <v>37.72</v>
@@ -702,7 +702,7 @@
         <v>37.7</v>
       </c>
       <c r="O3" t="n">
-        <v>611233495000</v>
+        <v>620061812950</v>
       </c>
       <c r="P3" t="n">
         <v>67300</v>
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>7260</v>
+        <v>7320</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+9.01%</t>
+          <t>'+9.91%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="F4" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G4" t="n">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
@@ -794,7 +794,7 @@
         <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>9409827240</v>
+        <v>9509150890</v>
       </c>
       <c r="P4" t="n">
         <v>8430</v>
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1673</v>
+        <v>1660</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+3.91%</t>
+          <t>'+3.11%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>-0.39</v>
       </c>
       <c r="E5" t="n">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="F5" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="G5" t="n">
-        <v>262</v>
+        <v>268</v>
       </c>
       <c r="H5" t="n">
         <v>0.3</v>
@@ -886,7 +886,7 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="O5" t="n">
-        <v>23048999519</v>
+        <v>23245571044</v>
       </c>
       <c r="P5" t="n">
         <v>3980</v>
@@ -902,16 +902,16 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>보호예수 해제 물량 및 주가조작 의혹 언급. 긍정적 호재와 단기 차익 가능성 제기.</t>
+          <t>주가 조작 의혹 제기 및 하락세 지속. 보호예수 해제 물량 부담, 단타 세력의 움직임에 대한 관망세.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['보호예수 해제', '주가 조작', '호재']</t>
+          <t>['주가 조작', '하락세', '보호예수 해제']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -931,267 +931,267 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>앤로보틱스</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1627</v>
+        <v>14510</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'-1.51%</t>
+          <t>'-1.76%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>-0.02</v>
+        <v>0.13</v>
       </c>
       <c r="E6" t="n">
-        <v>80</v>
+        <v>151</v>
       </c>
       <c r="F6" t="n">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="G6" t="n">
-        <v>130</v>
+        <v>296</v>
       </c>
       <c r="H6" t="n">
-        <v>5.01</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>1652</v>
+        <v>14770</v>
       </c>
       <c r="K6" t="n">
-        <v>1715</v>
+        <v>14770</v>
       </c>
       <c r="L6" t="n">
-        <v>1830</v>
+        <v>15290</v>
       </c>
       <c r="M6" t="n">
-        <v>1611</v>
+        <v>14470</v>
       </c>
       <c r="N6" t="n">
-        <v>5.03</v>
+        <v>9.82</v>
       </c>
       <c r="O6" t="n">
-        <v>29341707678</v>
+        <v>42094333610</v>
       </c>
       <c r="P6" t="n">
-        <v>4980</v>
+        <v>40350</v>
       </c>
       <c r="Q6" t="n">
-        <v>735</v>
+        <v>3320</v>
       </c>
       <c r="R6" t="n">
-        <v>-49000</v>
+        <v>97000</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>-79000</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>앤로보틱스, 단기 급등 후 조정 국면. 일부 긍정적 전망과 함께 변동성에 대한 언급.</t>
+          <t>실적 우량주 언급과 함께 외국인·연기금 매수세 포착. 정치 관련 언급 및 삼성E&amp;A와의 비교.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['단기 급등', '변동성', '조정']</t>
+          <t>['건설주', '외국인 매수', '실적']</t>
         </is>
       </c>
       <c r="X6" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>138360</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>앤로보틱스</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>14530</v>
+        <v>1621</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'-1.62%</t>
+          <t>'-1.88%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.13</v>
+        <v>-0.02</v>
       </c>
       <c r="E7" t="n">
-        <v>148</v>
+        <v>83</v>
       </c>
       <c r="F7" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="G7" t="n">
-        <v>276</v>
+        <v>139</v>
       </c>
       <c r="H7" t="n">
-        <v>9.949999999999999</v>
+        <v>5.01</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>14770</v>
+        <v>1652</v>
       </c>
       <c r="K7" t="n">
-        <v>14770</v>
+        <v>1715</v>
       </c>
       <c r="L7" t="n">
-        <v>15290</v>
+        <v>1830</v>
       </c>
       <c r="M7" t="n">
-        <v>14470</v>
+        <v>1611</v>
       </c>
       <c r="N7" t="n">
-        <v>9.82</v>
+        <v>5.03</v>
       </c>
       <c r="O7" t="n">
-        <v>41538394660</v>
+        <v>29563546563</v>
       </c>
       <c r="P7" t="n">
-        <v>40350</v>
+        <v>4980</v>
       </c>
       <c r="Q7" t="n">
-        <v>3320</v>
+        <v>735</v>
       </c>
       <c r="R7" t="n">
-        <v>97000</v>
+        <v>-49000</v>
       </c>
       <c r="S7" t="n">
-        <v>-79000</v>
+        <v>0</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>실적 우량주 언급과 함께 외국인·연기금 매수세 포착. 정치 관련 언급 및 삼성E&amp;A와의 비교.</t>
+          <t>앤로보틱스, 단기 급등 후 조정 국면. 일부 긍정적 전망과 함께 변동성에 대한 언급.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['건설주', '외국인 매수', '실적']</t>
+          <t>['단기 급등', '변동성', '조정']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>138360</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>LG디스플레이</t>
+          <t>HLB</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>7230</v>
+        <v>41450</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'-1.63%</t>
+          <t>'-2.13%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.02</v>
+        <v>-0.14</v>
       </c>
       <c r="E8" t="n">
-        <v>195</v>
+        <v>218</v>
       </c>
       <c r="F8" t="n">
-        <v>83</v>
+        <v>109</v>
       </c>
       <c r="G8" t="n">
-        <v>796</v>
+        <v>919</v>
       </c>
       <c r="H8" t="n">
-        <v>25.47</v>
+        <v>13.09</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>7350</v>
+        <v>42350</v>
       </c>
       <c r="K8" t="n">
-        <v>7270</v>
+        <v>41850</v>
       </c>
       <c r="L8" t="n">
-        <v>7350</v>
+        <v>42350</v>
       </c>
       <c r="M8" t="n">
-        <v>7120</v>
+        <v>41150</v>
       </c>
       <c r="N8" t="n">
-        <v>25.45</v>
+        <v>13.23</v>
       </c>
       <c r="O8" t="n">
-        <v>19348228220</v>
+        <v>15056695225</v>
       </c>
       <c r="P8" t="n">
-        <v>17950</v>
+        <v>69200</v>
       </c>
       <c r="Q8" t="n">
-        <v>7120</v>
+        <v>24150</v>
       </c>
       <c r="R8" t="n">
-        <v>-80000</v>
+        <v>47000</v>
       </c>
       <c r="S8" t="n">
-        <v>-92000</v>
+        <v>0</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>적자에서 흑자 전환 및 순이익 증가 등 긍정적 실적 발표. 주가 상승 기대감.</t>
+          <t>FDA 승인 관련 불확실성 속 기대감과 우려 공존, Class 1 또는 Class 2 승인 가능성에 대한 논쟁.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['흑자 전환', '순이익', '실적 발표']</t>
+          <t>['FDA', '승인', 'Class']</t>
         </is>
       </c>
       <c r="X8" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
@@ -1200,90 +1200,90 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>034220</t>
+          <t>028300</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>HLB</t>
+          <t>LG디스플레이</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>41500</v>
+        <v>7190</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'-2.01%</t>
+          <t>'-2.18%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-0.14</v>
+        <v>0.02</v>
       </c>
       <c r="E9" t="n">
-        <v>215</v>
+        <v>200</v>
       </c>
       <c r="F9" t="n">
-        <v>107</v>
+        <v>85</v>
       </c>
       <c r="G9" t="n">
-        <v>912</v>
+        <v>813</v>
       </c>
       <c r="H9" t="n">
-        <v>13.09</v>
+        <v>25.47</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>42350</v>
+        <v>7350</v>
       </c>
       <c r="K9" t="n">
-        <v>41850</v>
+        <v>7270</v>
       </c>
       <c r="L9" t="n">
-        <v>42350</v>
+        <v>7350</v>
       </c>
       <c r="M9" t="n">
-        <v>41150</v>
+        <v>7120</v>
       </c>
       <c r="N9" t="n">
-        <v>13.23</v>
+        <v>25.45</v>
       </c>
       <c r="O9" t="n">
-        <v>14340989825</v>
+        <v>20133876770</v>
       </c>
       <c r="P9" t="n">
-        <v>69200</v>
+        <v>17950</v>
       </c>
       <c r="Q9" t="n">
-        <v>24150</v>
+        <v>7120</v>
       </c>
       <c r="R9" t="n">
-        <v>47000</v>
+        <v>-80000</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>-92000</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>FDA 승인 관련 불확실성 속 기대감과 우려 공존, Class 1 또는 Class 2 승인 가능성에 대한 논쟁.</t>
+          <t>적자에서 흑자 전환 및 턴어라운드 기대감. 7천억대 당기순이익, 순이익 증가율 호조. 주주 평균단가 대비 저평가 주장.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['FDA', '승인', 'Class']</t>
+          <t>['흑자 전환', '턴어라운드', '당기순이익']</t>
         </is>
       </c>
       <c r="X9" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
@@ -1292,86 +1292,86 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>028300</t>
+          <t>034220</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>명신산업</t>
+          <t>라온시큐어</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>9930</v>
+        <v>17500</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'-2.55%</t>
+          <t>'-2.34%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.53</v>
+        <v>-0.32</v>
       </c>
       <c r="E10" t="n">
-        <v>140</v>
+        <v>109</v>
       </c>
       <c r="F10" t="n">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="G10" t="n">
-        <v>394</v>
+        <v>147</v>
       </c>
       <c r="H10" t="n">
-        <v>5.87</v>
+        <v>3.29</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>10190</v>
+        <v>17920</v>
       </c>
       <c r="K10" t="n">
-        <v>10110</v>
+        <v>19180</v>
       </c>
       <c r="L10" t="n">
-        <v>10180</v>
+        <v>20150</v>
       </c>
       <c r="M10" t="n">
-        <v>9620</v>
+        <v>17060</v>
       </c>
       <c r="N10" t="n">
-        <v>5.34</v>
+        <v>3.61</v>
       </c>
       <c r="O10" t="n">
-        <v>18120241185</v>
+        <v>80134185270</v>
       </c>
       <c r="P10" t="n">
-        <v>14940</v>
+        <v>22450</v>
       </c>
       <c r="Q10" t="n">
-        <v>5390</v>
+        <v>6320</v>
       </c>
       <c r="R10" t="n">
-        <v>-10000</v>
+        <v>-20000</v>
       </c>
       <c r="S10" t="n">
-        <v>33000</v>
+        <v>0</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>테슬라 실적 호조 및 스페이스X 관련 뉴스에 따른 긍정적 전망, 단기적 하락 국면에서의 저점 매수 기회 탐색.</t>
+          <t>라온시큐어, 미국 보안주 급등 및 해킹 이슈 확산에 따른 관심 증가. 전고점 돌파 기대감 및 보안 스테이블코인 관련 언급.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['테슬라', '스페이스X']</t>
+          <t>['보안 이슈', '해킹', '전고점 돌파']</t>
         </is>
       </c>
       <c r="X10" t="n">
@@ -1379,91 +1379,91 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>009900</t>
+          <t>042510</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>라온시큐어</t>
+          <t>명신산업</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>17310</v>
+        <v>9930</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'-3.40%</t>
+          <t>'-2.55%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>-0.32</v>
+        <v>0.53</v>
       </c>
       <c r="E11" t="n">
-        <v>107</v>
+        <v>141</v>
       </c>
       <c r="F11" t="n">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="G11" t="n">
-        <v>143</v>
+        <v>397</v>
       </c>
       <c r="H11" t="n">
-        <v>3.29</v>
+        <v>5.87</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>17920</v>
+        <v>10190</v>
       </c>
       <c r="K11" t="n">
-        <v>19180</v>
+        <v>10110</v>
       </c>
       <c r="L11" t="n">
-        <v>20150</v>
+        <v>10180</v>
       </c>
       <c r="M11" t="n">
-        <v>17060</v>
+        <v>9620</v>
       </c>
       <c r="N11" t="n">
-        <v>3.61</v>
+        <v>5.34</v>
       </c>
       <c r="O11" t="n">
-        <v>78905284470</v>
+        <v>18430859090</v>
       </c>
       <c r="P11" t="n">
-        <v>22450</v>
+        <v>14940</v>
       </c>
       <c r="Q11" t="n">
-        <v>6320</v>
+        <v>5390</v>
       </c>
       <c r="R11" t="n">
-        <v>-20000</v>
+        <v>-10000</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>33000</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>라온시큐어, 미국 보안주 급등 및 해킹 이슈 확산에 따른 관심 증가. 전고점 돌파 기대감 및 보안 스테이블코인 관련 언급.</t>
+          <t>테슬라 실적 호조 및 스페이스X 관련 뉴스에 따른 긍정적 전망, 단기적 하락 국면에서의 저점 매수 기회 탐색.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['보안 이슈', '해킹', '전고점 돌파']</t>
+          <t>['테슬라', '스페이스X']</t>
         </is>
       </c>
       <c r="X11" t="n">
@@ -1471,12 +1471,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>042510</t>
+          <t>009900</t>
         </is>
       </c>
     </row>
@@ -1487,11 +1487,11 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>214250</v>
+        <v>214750</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-4.14%</t>
+          <t>'-3.91%</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -1501,10 +1501,10 @@
         <v>800</v>
       </c>
       <c r="F12" t="n">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="G12" t="n">
-        <v>1588</v>
+        <v>1573</v>
       </c>
       <c r="H12" t="n">
         <v>46.14</v>
@@ -1530,7 +1530,7 @@
         <v>46.08</v>
       </c>
       <c r="O12" t="n">
-        <v>2044572742000</v>
+        <v>2113104630000</v>
       </c>
       <c r="P12" t="n">
         <v>374500</v>
@@ -1546,7 +1546,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>현 정부의 정책 실패와 주가 하락에 대한 불만을 표출하며, 정치적 이슈에 대한 부정적 감정 확산.</t>
+          <t>정치적 이슈로 인한 주가 하락 및 정부 대책 부재에 대한 불만 고조. 엔비디아, 마이크론 대비 한국 주식 하락세 지적.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
@@ -1555,7 +1555,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['주가 하락', '정부 대책', '정치적 이슈']</t>
         </is>
       </c>
       <c r="X12" t="n">
@@ -1579,11 +1579,11 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1221000</v>
+        <v>1220000</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'-5.64%</t>
+          <t>'-5.72%</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -1593,10 +1593,10 @@
         <v>800</v>
       </c>
       <c r="F13" t="n">
-        <v>542</v>
+        <v>536</v>
       </c>
       <c r="G13" t="n">
-        <v>1946</v>
+        <v>1944</v>
       </c>
       <c r="H13" t="n">
         <v>48.79</v>
@@ -1622,7 +1622,7 @@
         <v>48.77</v>
       </c>
       <c r="O13" t="n">
-        <v>2581650886500</v>
+        <v>2683931964500</v>
       </c>
       <c r="P13" t="n">
         <v>2987000</v>
@@ -1638,7 +1638,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>현 정부의 정책 실패와 최태원 회장의 행보에 대한 강한 비판 및 불만으로, 주가 하락에 대한 부정적 정서 심화.</t>
+          <t>정치적 이슈(이재명 정부, 최태원 회장)에 대한 강한 불만 표출 및 주가 하락 책임 전가. 투자자들의 막대한 손실 경험 공유.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
@@ -1647,7 +1647,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['정치적 이슈', '주가 하락', '손실']</t>
         </is>
       </c>
       <c r="X13" t="n">
@@ -1667,31 +1667,31 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>멜콘</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>14100</v>
+        <v>13330</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-5.87%</t>
+          <t>'-6.85%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>1.2</v>
+        <v>0.33</v>
       </c>
       <c r="E14" t="n">
-        <v>119</v>
+        <v>150</v>
       </c>
       <c r="F14" t="n">
-        <v>59</v>
+        <v>90</v>
       </c>
       <c r="G14" t="n">
-        <v>224</v>
+        <v>616</v>
       </c>
       <c r="H14" t="n">
-        <v>1.2</v>
+        <v>3.48</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1699,91 +1699,91 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>14980</v>
+        <v>14310</v>
       </c>
       <c r="K14" t="n">
-        <v>14460</v>
+        <v>14180</v>
       </c>
       <c r="L14" t="n">
-        <v>16140</v>
+        <v>14830</v>
       </c>
       <c r="M14" t="n">
-        <v>13550</v>
+        <v>13240</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="O14" t="n">
-        <v>83299262795</v>
+        <v>120221835685</v>
       </c>
       <c r="P14" t="n">
-        <v>28800</v>
+        <v>31500</v>
       </c>
       <c r="Q14" t="n">
-        <v>12030</v>
+        <v>1640</v>
       </c>
       <c r="R14" t="n">
-        <v>-54000</v>
+        <v>-354000</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>-155000</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>반도체 및 AI 관련 뉴스 언급. 보호예수 해제일 전후의 주가 변동성 관찰. ASML 협력 관련 내용.</t>
+          <t>EUV용 유리기판 제조 기술 확보 및 AI 광통신 관련 뉴스 부각. 전세계 AI 광통신 열풍 속 기대감 형성. 그러나 계단식 하락 추세 및 프로그램 매도세 언급.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['반도체', 'AI', '보호예수']</t>
+          <t>['EUV 유리기판', 'AI 광통신', '기술 확보']</t>
         </is>
       </c>
       <c r="X14" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>179880</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>멜콘</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>13400</v>
+        <v>13850</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-6.36%</t>
+          <t>'-7.54%</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>0.33</v>
+        <v>1.2</v>
       </c>
       <c r="E15" t="n">
-        <v>152</v>
+        <v>119</v>
       </c>
       <c r="F15" t="n">
-        <v>90</v>
+        <v>59</v>
       </c>
       <c r="G15" t="n">
-        <v>623</v>
+        <v>228</v>
       </c>
       <c r="H15" t="n">
-        <v>3.48</v>
+        <v>1.2</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1791,60 +1791,60 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>14310</v>
+        <v>14980</v>
       </c>
       <c r="K15" t="n">
-        <v>14180</v>
+        <v>14460</v>
       </c>
       <c r="L15" t="n">
-        <v>14830</v>
+        <v>16140</v>
       </c>
       <c r="M15" t="n">
-        <v>13240</v>
+        <v>13550</v>
       </c>
       <c r="N15" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>118638626305</v>
+        <v>83835040055</v>
       </c>
       <c r="P15" t="n">
-        <v>31500</v>
+        <v>28800</v>
       </c>
       <c r="Q15" t="n">
-        <v>1640</v>
+        <v>12030</v>
       </c>
       <c r="R15" t="n">
-        <v>-354000</v>
+        <v>-54000</v>
       </c>
       <c r="S15" t="n">
-        <v>-155000</v>
+        <v>0</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>EUV용 유리기판 제조 기술 확보 및 AI 광통신 관련 뉴스. 삼성 인수설 등으로 인한 기대감 형성.</t>
+          <t>반도체 및 AI 관련 뉴스 언급. 보호예수 해제일 전후의 주가 변동성 관찰. ASML 협력 관련 내용.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['EUV 유리기판', 'AI 광통신', '기술 확보']</t>
+          <t>['반도체', 'AI', '보호예수']</t>
         </is>
       </c>
       <c r="X15" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>179880</t>
         </is>
       </c>
     </row>
@@ -1866,13 +1866,13 @@
         <v>2.41</v>
       </c>
       <c r="E16" t="n">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="F16" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="G16" t="n">
-        <v>530</v>
+        <v>535</v>
       </c>
       <c r="H16" t="n">
         <v>3.69</v>
@@ -1898,7 +1898,7 @@
         <v>1.28</v>
       </c>
       <c r="O16" t="n">
-        <v>63973438215</v>
+        <v>64463333755</v>
       </c>
       <c r="P16" t="n">
         <v>11690</v>
@@ -1914,16 +1914,16 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>주가 급락 및 조정에 대한 부정적 의견. 투자 경고 및 신용 사용 자제 권고.</t>
+          <t>투기예고, 급락 가능성에 대한 우려. 외국인 허매수 후 매도, 개미 물량 증가. ESS 마진율 불확실성 언급.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['주가 급락', '조정', '투기']</t>
+          <t>['투기예고', '급락', '외국인 매도']</t>
         </is>
       </c>
       <c r="X16" t="n">

--- a/data/trending_integrated_20261022_15.xlsx
+++ b/data/trending_integrated_20261022_15.xlsx
@@ -567,24 +567,24 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3675</v>
+        <v>3750</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+18.93%</t>
+          <t>'+21.36%</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>365</v>
+        <v>375</v>
       </c>
       <c r="F2" t="n">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="G2" t="n">
-        <v>924</v>
+        <v>928</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -610,7 +610,7 @@
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>88757121995</v>
+        <v>91368865061</v>
       </c>
       <c r="P2" t="n">
         <v>7050</v>
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>55000</v>
+        <v>55500</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+15.30%</t>
+          <t>'+16.35%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>0.02</v>
       </c>
       <c r="E3" t="n">
-        <v>372</v>
+        <v>379</v>
       </c>
       <c r="F3" t="n">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="G3" t="n">
-        <v>1536</v>
+        <v>1580</v>
       </c>
       <c r="H3" t="n">
         <v>37.72</v>
@@ -702,7 +702,7 @@
         <v>37.7</v>
       </c>
       <c r="O3" t="n">
-        <v>620061812950</v>
+        <v>627874319300</v>
       </c>
       <c r="P3" t="n">
         <v>67300</v>
@@ -718,7 +718,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>실적 발표 및 어닝 서프라이즈, 자사주 취득 공시로 강한 상승세 전망. MSCI 편입 예상.</t>
+          <t>어닝 서프라이즈 실적 발표 및 자사주 취득, MSCI 편입 예상 등 긍정적 요인 다수 확인. 공매도 감소 기대.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>7320</v>
+        <v>7310</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+9.91%</t>
+          <t>'+9.76%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="F4" t="n">
         <v>32</v>
       </c>
       <c r="G4" t="n">
-        <v>175</v>
+        <v>184</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
@@ -794,7 +794,7 @@
         <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>9509150890</v>
+        <v>9615664785</v>
       </c>
       <c r="P4" t="n">
         <v>8430</v>
@@ -810,16 +810,16 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>루미아 인수 및 로봇 사업 관련 구체적인 뉴스, 외인 매수세 유입으로 인한 급등 기대감 형성.</t>
+          <t>자회사 루미아의 로봇 사업 관련 뉴스 및 구체적인 기술 개발 내용 언급. 외인 대량 매수 확인, 향후 주가 상승 기대감 높음.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['루미아', '촉각 센서', '신주인수권']</t>
+          <t>['루미아', '촉각 센서', '외인 매수']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -854,13 +854,13 @@
         <v>-0.39</v>
       </c>
       <c r="E5" t="n">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="F5" t="n">
         <v>61</v>
       </c>
       <c r="G5" t="n">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="H5" t="n">
         <v>0.3</v>
@@ -886,7 +886,7 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="O5" t="n">
-        <v>23245571044</v>
+        <v>23342896360</v>
       </c>
       <c r="P5" t="n">
         <v>3980</v>
@@ -935,24 +935,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>14510</v>
+        <v>14560</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'-1.76%</t>
+          <t>'-1.42%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>0.13</v>
       </c>
       <c r="E6" t="n">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="F6" t="n">
         <v>49</v>
       </c>
       <c r="G6" t="n">
-        <v>296</v>
+        <v>307</v>
       </c>
       <c r="H6" t="n">
         <v>9.949999999999999</v>
@@ -978,7 +978,7 @@
         <v>9.82</v>
       </c>
       <c r="O6" t="n">
-        <v>42094333610</v>
+        <v>42575361195</v>
       </c>
       <c r="P6" t="n">
         <v>40350</v>
@@ -994,16 +994,16 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>실적 우량주 언급과 함께 외국인·연기금 매수세 포착. 정치 관련 언급 및 삼성E&amp;A와의 비교.</t>
+          <t>정치적 이슈와 관련된 부정적 언급이 다수이며, 특정 세력에 의한 주가 하락 및 조작 의혹 제기.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['건설주', '외국인 매수', '실적']</t>
+          <t>['정치적 이슈', '주가 조작', '공매도']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1027,18 +1027,18 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1621</v>
+        <v>1624</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'-1.88%</t>
+          <t>'-1.69%</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>-0.02</v>
       </c>
       <c r="E7" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="F7" t="n">
         <v>40</v>
@@ -1070,7 +1070,7 @@
         <v>5.03</v>
       </c>
       <c r="O7" t="n">
-        <v>29563546563</v>
+        <v>29733940268</v>
       </c>
       <c r="P7" t="n">
         <v>4980</v>
@@ -1115,83 +1115,83 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>HLB</t>
+          <t>LG디스플레이</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>41450</v>
+        <v>7220</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'-2.13%</t>
+          <t>'-1.77%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>-0.14</v>
+        <v>0.02</v>
       </c>
       <c r="E8" t="n">
-        <v>218</v>
+        <v>206</v>
       </c>
       <c r="F8" t="n">
-        <v>109</v>
+        <v>85</v>
       </c>
       <c r="G8" t="n">
-        <v>919</v>
+        <v>833</v>
       </c>
       <c r="H8" t="n">
-        <v>13.09</v>
+        <v>25.47</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>42350</v>
+        <v>7350</v>
       </c>
       <c r="K8" t="n">
-        <v>41850</v>
+        <v>7270</v>
       </c>
       <c r="L8" t="n">
-        <v>42350</v>
+        <v>7350</v>
       </c>
       <c r="M8" t="n">
-        <v>41150</v>
+        <v>7120</v>
       </c>
       <c r="N8" t="n">
-        <v>13.23</v>
+        <v>25.45</v>
       </c>
       <c r="O8" t="n">
-        <v>15056695225</v>
+        <v>20722434245</v>
       </c>
       <c r="P8" t="n">
-        <v>69200</v>
+        <v>17950</v>
       </c>
       <c r="Q8" t="n">
-        <v>24150</v>
+        <v>7120</v>
       </c>
       <c r="R8" t="n">
-        <v>47000</v>
+        <v>-80000</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>-92000</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>FDA 승인 관련 불확실성 속 기대감과 우려 공존, Class 1 또는 Class 2 승인 가능성에 대한 논쟁.</t>
+          <t>적자에서 흑자 전환 및 순이익 증가 등 긍정적 실적 지표 확인. 다만, 주가 움직임에 대한 아쉬움 표출.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['FDA', '승인', 'Class']</t>
+          <t>['흑자 전환', '순이익 증가', '실적 개선']</t>
         </is>
       </c>
       <c r="X8" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
@@ -1200,90 +1200,90 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>028300</t>
+          <t>034220</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>LG디스플레이</t>
+          <t>HLB</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>7190</v>
+        <v>41400</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'-2.18%</t>
+          <t>'-2.24%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.02</v>
+        <v>-0.14</v>
       </c>
       <c r="E9" t="n">
-        <v>200</v>
+        <v>218</v>
       </c>
       <c r="F9" t="n">
-        <v>85</v>
+        <v>109</v>
       </c>
       <c r="G9" t="n">
-        <v>813</v>
+        <v>931</v>
       </c>
       <c r="H9" t="n">
-        <v>25.47</v>
+        <v>13.09</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>7350</v>
+        <v>42350</v>
       </c>
       <c r="K9" t="n">
-        <v>7270</v>
+        <v>41850</v>
       </c>
       <c r="L9" t="n">
-        <v>7350</v>
+        <v>42350</v>
       </c>
       <c r="M9" t="n">
-        <v>7120</v>
+        <v>41150</v>
       </c>
       <c r="N9" t="n">
-        <v>25.45</v>
+        <v>13.23</v>
       </c>
       <c r="O9" t="n">
-        <v>20133876770</v>
+        <v>15624394425</v>
       </c>
       <c r="P9" t="n">
-        <v>17950</v>
+        <v>69200</v>
       </c>
       <c r="Q9" t="n">
-        <v>7120</v>
+        <v>24150</v>
       </c>
       <c r="R9" t="n">
-        <v>-80000</v>
+        <v>47000</v>
       </c>
       <c r="S9" t="n">
-        <v>-92000</v>
+        <v>0</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>적자에서 흑자 전환 및 턴어라운드 기대감. 7천억대 당기순이익, 순이익 증가율 호조. 주주 평균단가 대비 저평가 주장.</t>
+          <t>FDA 승인 관련 불확실성 속 기대감과 우려 공존, Class 1 또는 Class 2 승인 가능성에 대한 논쟁.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['흑자 전환', '턴어라운드', '당기순이익']</t>
+          <t>['FDA', '승인', 'Class']</t>
         </is>
       </c>
       <c r="X9" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
@@ -1292,7 +1292,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>034220</t>
+          <t>028300</t>
         </is>
       </c>
     </row>
@@ -1303,24 +1303,24 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>17500</v>
+        <v>17480</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'-2.34%</t>
+          <t>'-2.46%</t>
         </is>
       </c>
       <c r="D10" t="n">
         <v>-0.32</v>
       </c>
       <c r="E10" t="n">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="F10" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G10" t="n">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="H10" t="n">
         <v>3.29</v>
@@ -1346,7 +1346,7 @@
         <v>3.61</v>
       </c>
       <c r="O10" t="n">
-        <v>80134185270</v>
+        <v>80786371095</v>
       </c>
       <c r="P10" t="n">
         <v>22450</v>
@@ -1395,11 +1395,11 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>9930</v>
+        <v>9900</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'-2.55%</t>
+          <t>'-2.85%</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -1412,7 +1412,7 @@
         <v>65</v>
       </c>
       <c r="G11" t="n">
-        <v>397</v>
+        <v>406</v>
       </c>
       <c r="H11" t="n">
         <v>5.87</v>
@@ -1438,7 +1438,7 @@
         <v>5.34</v>
       </c>
       <c r="O11" t="n">
-        <v>18430859090</v>
+        <v>18704838380</v>
       </c>
       <c r="P11" t="n">
         <v>14940</v>
@@ -1454,7 +1454,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>테슬라 실적 호조 및 스페이스X 관련 뉴스에 따른 긍정적 전망, 단기적 하락 국면에서의 저점 매수 기회 탐색.</t>
+          <t>테슬라 실적 상회 및 스페이스X 관련 뉴스 언급. 코스피 지수 하락 속에서 상대적 선방 및 개미 털기 가능성 제기.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
@@ -1463,7 +1463,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['테슬라', '스페이스X']</t>
+          <t>['테슬라', '스페이스X', '개미 털기']</t>
         </is>
       </c>
       <c r="X11" t="n">
@@ -1487,11 +1487,11 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>214750</v>
+        <v>215500</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-3.91%</t>
+          <t>'-3.58%</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -1501,10 +1501,10 @@
         <v>800</v>
       </c>
       <c r="F12" t="n">
-        <v>526</v>
+        <v>534</v>
       </c>
       <c r="G12" t="n">
-        <v>1573</v>
+        <v>1632</v>
       </c>
       <c r="H12" t="n">
         <v>46.14</v>
@@ -1530,7 +1530,7 @@
         <v>46.08</v>
       </c>
       <c r="O12" t="n">
-        <v>2113104630000</v>
+        <v>2162292208500</v>
       </c>
       <c r="P12" t="n">
         <v>374500</v>
@@ -1546,16 +1546,16 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>정치적 이슈로 인한 주가 하락 및 정부 대책 부재에 대한 불만 고조. 엔비디아, 마이크론 대비 한국 주식 하락세 지적.</t>
+          <t>정치적 이슈에 대한 부정적 언급이 주를 이루며, 시장 상황 및 타 반도체 종목 대비 하락에 대한 불만 제기.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['주가 하락', '정부 대책', '정치적 이슈']</t>
+          <t>['정치적 이슈', '시장 상황', '주가 하락']</t>
         </is>
       </c>
       <c r="X12" t="n">
@@ -1593,10 +1593,10 @@
         <v>800</v>
       </c>
       <c r="F13" t="n">
-        <v>536</v>
+        <v>532</v>
       </c>
       <c r="G13" t="n">
-        <v>1944</v>
+        <v>1991</v>
       </c>
       <c r="H13" t="n">
         <v>48.79</v>
@@ -1622,7 +1622,7 @@
         <v>48.77</v>
       </c>
       <c r="O13" t="n">
-        <v>2683931964500</v>
+        <v>2748164797000</v>
       </c>
       <c r="P13" t="n">
         <v>2987000</v>
@@ -1638,16 +1638,16 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>정치적 이슈(이재명 정부, 최태원 회장)에 대한 강한 불만 표출 및 주가 하락 책임 전가. 투자자들의 막대한 손실 경험 공유.</t>
+          <t>정치적 이슈 및 정부 정책에 대한 강한 불만 표출. 전반적인 시장 하락 및 개인 투자자 손실 심화 우려.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['정치적 이슈', '주가 하락', '손실']</t>
+          <t>['정치적 이슈', '시장 하락', '투자 손실']</t>
         </is>
       </c>
       <c r="X13" t="n">
@@ -1671,24 +1671,24 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>13330</v>
+        <v>13340</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-6.85%</t>
+          <t>'-6.78%</t>
         </is>
       </c>
       <c r="D14" t="n">
         <v>0.33</v>
       </c>
       <c r="E14" t="n">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="F14" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="G14" t="n">
-        <v>616</v>
+        <v>620</v>
       </c>
       <c r="H14" t="n">
         <v>3.48</v>
@@ -1714,7 +1714,7 @@
         <v>3.15</v>
       </c>
       <c r="O14" t="n">
-        <v>120221835685</v>
+        <v>121054735595</v>
       </c>
       <c r="P14" t="n">
         <v>31500</v>
@@ -1763,24 +1763,24 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>13850</v>
+        <v>13590</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-7.54%</t>
+          <t>'-9.28%</t>
         </is>
       </c>
       <c r="D15" t="n">
         <v>1.2</v>
       </c>
       <c r="E15" t="n">
-        <v>119</v>
+        <v>127</v>
       </c>
       <c r="F15" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="G15" t="n">
-        <v>228</v>
+        <v>247</v>
       </c>
       <c r="H15" t="n">
         <v>1.2</v>
@@ -1806,7 +1806,7 @@
         <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>83835040055</v>
+        <v>84766396830</v>
       </c>
       <c r="P15" t="n">
         <v>28800</v>
@@ -1822,16 +1822,16 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>반도체 및 AI 관련 뉴스 언급. 보호예수 해제일 전후의 주가 변동성 관찰. ASML 협력 관련 내용.</t>
+          <t>보호예수 해제 및 주가 하락에 대한 우려 표출. 빅웨이브 등 타 종목 언급.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['반도체', 'AI', '보호예수']</t>
+          <t>['보호예수', '주가 하락', '빅웨이브']</t>
         </is>
       </c>
       <c r="X15" t="n">
@@ -1839,7 +1839,7 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
@@ -1855,24 +1855,24 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>10010</v>
+        <v>10090</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'-10.14%</t>
+          <t>'-9.43%</t>
         </is>
       </c>
       <c r="D16" t="n">
         <v>2.41</v>
       </c>
       <c r="E16" t="n">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="F16" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="G16" t="n">
-        <v>535</v>
+        <v>544</v>
       </c>
       <c r="H16" t="n">
         <v>3.69</v>
@@ -1898,7 +1898,7 @@
         <v>1.28</v>
       </c>
       <c r="O16" t="n">
-        <v>64463333755</v>
+        <v>65512541795</v>
       </c>
       <c r="P16" t="n">
         <v>11690</v>

--- a/data/trending_integrated_20261022_15.xlsx
+++ b/data/trending_integrated_20261022_15.xlsx
@@ -578,13 +578,13 @@
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>375</v>
+        <v>383</v>
       </c>
       <c r="F2" t="n">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="G2" t="n">
-        <v>928</v>
+        <v>948</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -610,7 +610,7 @@
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>91368865061</v>
+        <v>92314967561</v>
       </c>
       <c r="P2" t="n">
         <v>7050</v>
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>55500</v>
+        <v>55400</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+16.35%</t>
+          <t>'+16.14%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>0.02</v>
       </c>
       <c r="E3" t="n">
-        <v>379</v>
+        <v>386</v>
       </c>
       <c r="F3" t="n">
-        <v>204</v>
+        <v>211</v>
       </c>
       <c r="G3" t="n">
-        <v>1580</v>
+        <v>1604</v>
       </c>
       <c r="H3" t="n">
         <v>37.72</v>
@@ -702,7 +702,7 @@
         <v>37.7</v>
       </c>
       <c r="O3" t="n">
-        <v>627874319300</v>
+        <v>633732924700</v>
       </c>
       <c r="P3" t="n">
         <v>67300</v>
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>7310</v>
+        <v>7330</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+9.76%</t>
+          <t>'+10.06%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="F4" t="n">
         <v>32</v>
       </c>
       <c r="G4" t="n">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
@@ -794,7 +794,7 @@
         <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>9615664785</v>
+        <v>9663346435</v>
       </c>
       <c r="P4" t="n">
         <v>8430</v>
@@ -810,16 +810,16 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>자회사 루미아의 로봇 사업 관련 뉴스 및 구체적인 기술 개발 내용 언급. 외인 대량 매수 확인, 향후 주가 상승 기대감 높음.</t>
+          <t>루미아와의 협력을 통한 촉각 센서 기술 개발 및 양산 기대감, 외인 매수세 유입 및 주가 상승 전망.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['루미아', '촉각 센서', '외인 매수']</t>
+          <t>['촉각 센서', '루미아', '외인매수']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1660</v>
+        <v>1658</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+3.11%</t>
+          <t>'+2.98%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>-0.39</v>
       </c>
       <c r="E5" t="n">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="F5" t="n">
         <v>61</v>
       </c>
       <c r="G5" t="n">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="H5" t="n">
         <v>0.3</v>
@@ -886,7 +886,7 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="O5" t="n">
-        <v>23342896360</v>
+        <v>23407692658</v>
       </c>
       <c r="P5" t="n">
         <v>3980</v>
@@ -931,184 +931,184 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>앤로보틱스</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>14560</v>
+        <v>1635</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'-1.42%</t>
+          <t>'-1.03%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.13</v>
+        <v>-0.02</v>
       </c>
       <c r="E6" t="n">
-        <v>154</v>
+        <v>85</v>
       </c>
       <c r="F6" t="n">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="G6" t="n">
-        <v>307</v>
+        <v>143</v>
       </c>
       <c r="H6" t="n">
-        <v>9.949999999999999</v>
+        <v>5.01</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>14770</v>
+        <v>1652</v>
       </c>
       <c r="K6" t="n">
-        <v>14770</v>
+        <v>1715</v>
       </c>
       <c r="L6" t="n">
-        <v>15290</v>
+        <v>1830</v>
       </c>
       <c r="M6" t="n">
-        <v>14470</v>
+        <v>1611</v>
       </c>
       <c r="N6" t="n">
-        <v>9.82</v>
+        <v>5.03</v>
       </c>
       <c r="O6" t="n">
-        <v>42575361195</v>
+        <v>29804166788</v>
       </c>
       <c r="P6" t="n">
-        <v>40350</v>
+        <v>4980</v>
       </c>
       <c r="Q6" t="n">
-        <v>3320</v>
+        <v>735</v>
       </c>
       <c r="R6" t="n">
-        <v>97000</v>
+        <v>-49000</v>
       </c>
       <c r="S6" t="n">
-        <v>-79000</v>
+        <v>0</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>정치적 이슈와 관련된 부정적 언급이 다수이며, 특정 세력에 의한 주가 하락 및 조작 의혹 제기.</t>
+          <t>앤로보틱스, 단기 급등 후 조정 국면. 일부 긍정적 전망과 함께 변동성에 대한 언급.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['정치적 이슈', '주가 조작', '공매도']</t>
+          <t>['단기 급등', '변동성', '조정']</t>
         </is>
       </c>
       <c r="X6" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>138360</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>앤로보틱스</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1624</v>
+        <v>14530</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'-1.69%</t>
+          <t>'-1.62%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>-0.02</v>
+        <v>0.13</v>
       </c>
       <c r="E7" t="n">
-        <v>84</v>
+        <v>158</v>
       </c>
       <c r="F7" t="n">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="G7" t="n">
-        <v>139</v>
+        <v>325</v>
       </c>
       <c r="H7" t="n">
-        <v>5.01</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>1652</v>
+        <v>14770</v>
       </c>
       <c r="K7" t="n">
-        <v>1715</v>
+        <v>14770</v>
       </c>
       <c r="L7" t="n">
-        <v>1830</v>
+        <v>15290</v>
       </c>
       <c r="M7" t="n">
-        <v>1611</v>
+        <v>14470</v>
       </c>
       <c r="N7" t="n">
-        <v>5.03</v>
+        <v>9.82</v>
       </c>
       <c r="O7" t="n">
-        <v>29733940268</v>
+        <v>43095418955</v>
       </c>
       <c r="P7" t="n">
-        <v>4980</v>
+        <v>40350</v>
       </c>
       <c r="Q7" t="n">
-        <v>735</v>
+        <v>3320</v>
       </c>
       <c r="R7" t="n">
-        <v>-49000</v>
+        <v>97000</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>-79000</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>앤로보틱스, 단기 급등 후 조정 국면. 일부 긍정적 전망과 함께 변동성에 대한 언급.</t>
+          <t>외국인 및 연기금 매수세 언급에도 불구하고 정치적 논란과 주가 조작 의혹 제기.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['단기 급등', '변동성', '조정']</t>
+          <t>['외국인', '연기금', '주가조작']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>138360</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
@@ -1119,24 +1119,24 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>7220</v>
+        <v>7230</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'-1.77%</t>
+          <t>'-1.63%</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>0.02</v>
       </c>
       <c r="E8" t="n">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="F8" t="n">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="G8" t="n">
-        <v>833</v>
+        <v>840</v>
       </c>
       <c r="H8" t="n">
         <v>25.47</v>
@@ -1162,7 +1162,7 @@
         <v>25.45</v>
       </c>
       <c r="O8" t="n">
-        <v>20722434245</v>
+        <v>22519523045</v>
       </c>
       <c r="P8" t="n">
         <v>17950</v>
@@ -1211,24 +1211,24 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>41400</v>
+        <v>41300</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'-2.24%</t>
+          <t>'-2.48%</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>-0.14</v>
       </c>
       <c r="E9" t="n">
-        <v>218</v>
+        <v>223</v>
       </c>
       <c r="F9" t="n">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="G9" t="n">
-        <v>931</v>
+        <v>945</v>
       </c>
       <c r="H9" t="n">
         <v>13.09</v>
@@ -1254,7 +1254,7 @@
         <v>13.23</v>
       </c>
       <c r="O9" t="n">
-        <v>15624394425</v>
+        <v>16088234725</v>
       </c>
       <c r="P9" t="n">
         <v>69200</v>
@@ -1299,79 +1299,79 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>라온시큐어</t>
+          <t>명신산업</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>17480</v>
+        <v>9890</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'-2.46%</t>
+          <t>'-2.94%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>-0.32</v>
+        <v>0.53</v>
       </c>
       <c r="E10" t="n">
-        <v>112</v>
+        <v>141</v>
       </c>
       <c r="F10" t="n">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="G10" t="n">
-        <v>149</v>
+        <v>406</v>
       </c>
       <c r="H10" t="n">
-        <v>3.29</v>
+        <v>5.87</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>17920</v>
+        <v>10190</v>
       </c>
       <c r="K10" t="n">
-        <v>19180</v>
+        <v>10110</v>
       </c>
       <c r="L10" t="n">
-        <v>20150</v>
+        <v>10180</v>
       </c>
       <c r="M10" t="n">
-        <v>17060</v>
+        <v>9620</v>
       </c>
       <c r="N10" t="n">
-        <v>3.61</v>
+        <v>5.34</v>
       </c>
       <c r="O10" t="n">
-        <v>80786371095</v>
+        <v>18981303440</v>
       </c>
       <c r="P10" t="n">
-        <v>22450</v>
+        <v>14940</v>
       </c>
       <c r="Q10" t="n">
-        <v>6320</v>
+        <v>5390</v>
       </c>
       <c r="R10" t="n">
-        <v>-20000</v>
+        <v>-10000</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>33000</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>라온시큐어, 미국 보안주 급등 및 해킹 이슈 확산에 따른 관심 증가. 전고점 돌파 기대감 및 보안 스테이블코인 관련 언급.</t>
+          <t>테슬라 실적 상회 및 스페이스X 관련 뉴스 언급. 코스피 지수 하락 속에서 상대적 선방 및 개미 털기 가능성 제기.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['보안 이슈', '해킹', '전고점 돌파']</t>
+          <t>['테슬라', '스페이스X', '개미 털기']</t>
         </is>
       </c>
       <c r="X10" t="n">
@@ -1379,91 +1379,91 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>042510</t>
+          <t>009900</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>명신산업</t>
+          <t>라온시큐어</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>9900</v>
+        <v>17350</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'-2.85%</t>
+          <t>'-3.18%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.53</v>
+        <v>-0.32</v>
       </c>
       <c r="E11" t="n">
-        <v>141</v>
+        <v>114</v>
       </c>
       <c r="F11" t="n">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="G11" t="n">
-        <v>406</v>
+        <v>153</v>
       </c>
       <c r="H11" t="n">
-        <v>5.87</v>
+        <v>3.29</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>10190</v>
+        <v>17920</v>
       </c>
       <c r="K11" t="n">
-        <v>10110</v>
+        <v>19180</v>
       </c>
       <c r="L11" t="n">
-        <v>10180</v>
+        <v>20150</v>
       </c>
       <c r="M11" t="n">
-        <v>9620</v>
+        <v>17060</v>
       </c>
       <c r="N11" t="n">
-        <v>5.34</v>
+        <v>3.61</v>
       </c>
       <c r="O11" t="n">
-        <v>18704838380</v>
+        <v>81266757895</v>
       </c>
       <c r="P11" t="n">
-        <v>14940</v>
+        <v>22450</v>
       </c>
       <c r="Q11" t="n">
-        <v>5390</v>
+        <v>6320</v>
       </c>
       <c r="R11" t="n">
-        <v>-10000</v>
+        <v>-20000</v>
       </c>
       <c r="S11" t="n">
-        <v>33000</v>
+        <v>0</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>테슬라 실적 상회 및 스페이스X 관련 뉴스 언급. 코스피 지수 하락 속에서 상대적 선방 및 개미 털기 가능성 제기.</t>
+          <t>라온시큐어, 미국 보안주 급등 및 해킹 이슈 확산에 따른 관심 증가. 전고점 돌파 기대감 및 보안 스테이블코인 관련 언급.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['테슬라', '스페이스X', '개미 털기']</t>
+          <t>['보안 이슈', '해킹', '전고점 돌파']</t>
         </is>
       </c>
       <c r="X11" t="n">
@@ -1471,12 +1471,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>009900</t>
+          <t>042510</t>
         </is>
       </c>
     </row>
@@ -1487,11 +1487,11 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>215500</v>
+        <v>214500</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-3.58%</t>
+          <t>'-4.03%</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -1501,10 +1501,10 @@
         <v>800</v>
       </c>
       <c r="F12" t="n">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="G12" t="n">
-        <v>1632</v>
+        <v>1686</v>
       </c>
       <c r="H12" t="n">
         <v>46.14</v>
@@ -1530,7 +1530,7 @@
         <v>46.08</v>
       </c>
       <c r="O12" t="n">
-        <v>2162292208500</v>
+        <v>2386242649500</v>
       </c>
       <c r="P12" t="n">
         <v>374500</v>
@@ -1546,16 +1546,16 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>정치적 이슈에 대한 부정적 언급이 주를 이루며, 시장 상황 및 타 반도체 종목 대비 하락에 대한 불만 제기.</t>
+          <t>정치적 불만 표출과 함께 주가 하락에 대한 부정적 감정 표현.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['정치적 이슈', '시장 상황', '주가 하락']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="X12" t="n">
@@ -1579,11 +1579,11 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1220000</v>
+        <v>1223000</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'-5.72%</t>
+          <t>'-5.49%</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -1593,10 +1593,10 @@
         <v>800</v>
       </c>
       <c r="F13" t="n">
-        <v>532</v>
+        <v>529</v>
       </c>
       <c r="G13" t="n">
-        <v>1991</v>
+        <v>1978</v>
       </c>
       <c r="H13" t="n">
         <v>48.79</v>
@@ -1622,7 +1622,7 @@
         <v>48.77</v>
       </c>
       <c r="O13" t="n">
-        <v>2748164797000</v>
+        <v>2988293509000</v>
       </c>
       <c r="P13" t="n">
         <v>2987000</v>
@@ -1638,16 +1638,16 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>정치적 이슈 및 정부 정책에 대한 강한 불만 표출. 전반적인 시장 하락 및 개인 투자자 손실 심화 우려.</t>
+          <t>정치적 불만과 경영진에 대한 강한 비판, 주가 하락에 대한 좌절감 표출.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['정치적 이슈', '시장 하락', '투자 손실']</t>
+          <t>['주가하락', '경영진', '손실']</t>
         </is>
       </c>
       <c r="X13" t="n">
@@ -1685,10 +1685,10 @@
         <v>151</v>
       </c>
       <c r="F14" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="G14" t="n">
-        <v>620</v>
+        <v>626</v>
       </c>
       <c r="H14" t="n">
         <v>3.48</v>
@@ -1714,7 +1714,7 @@
         <v>3.15</v>
       </c>
       <c r="O14" t="n">
-        <v>121054735595</v>
+        <v>121267175095</v>
       </c>
       <c r="P14" t="n">
         <v>31500</v>
@@ -1730,16 +1730,16 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>EUV용 유리기판 제조 기술 확보 및 AI 광통신 관련 뉴스 부각. 전세계 AI 광통신 열풍 속 기대감 형성. 그러나 계단식 하락 추세 및 프로그램 매도세 언급.</t>
+          <t>EUV용 유리기판 제조 기술 확보 및 AI 광통신 관련 긍정적 뉴스 언급, 주가 상승 기대.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['EUV 유리기판', 'AI 광통신', '기술 확보']</t>
+          <t>['EUV', '유리기판', 'AI']</t>
         </is>
       </c>
       <c r="X14" t="n">
@@ -1763,11 +1763,11 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>13590</v>
+        <v>13600</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-9.28%</t>
+          <t>'-9.21%</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -1780,7 +1780,7 @@
         <v>61</v>
       </c>
       <c r="G15" t="n">
-        <v>247</v>
+        <v>257</v>
       </c>
       <c r="H15" t="n">
         <v>1.2</v>
@@ -1806,7 +1806,7 @@
         <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>84766396830</v>
+        <v>84901254430</v>
       </c>
       <c r="P15" t="n">
         <v>28800</v>
@@ -1822,16 +1822,16 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>보호예수 해제 및 주가 하락에 대한 우려 표출. 빅웨이브 등 타 종목 언급.</t>
+          <t>주가 하락과 관련된 부정적 언급, 특정 종목 동반 하락 및 주포에 대한 불신 표출.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['보호예수', '주가 하락', '빅웨이브']</t>
+          <t>['주가하락', '보호예수', '주포']</t>
         </is>
       </c>
       <c r="X15" t="n">
@@ -1869,10 +1869,10 @@
         <v>198</v>
       </c>
       <c r="F16" t="n">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G16" t="n">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="H16" t="n">
         <v>3.69</v>
@@ -1898,7 +1898,7 @@
         <v>1.28</v>
       </c>
       <c r="O16" t="n">
-        <v>65512541795</v>
+        <v>66035092805</v>
       </c>
       <c r="P16" t="n">
         <v>11690</v>

--- a/data/trending_integrated_20261022_15.xlsx
+++ b/data/trending_integrated_20261022_15.xlsx
@@ -578,13 +578,13 @@
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="F2" t="n">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="G2" t="n">
-        <v>948</v>
+        <v>959</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -610,7 +610,7 @@
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>92314967561</v>
+        <v>92378121311</v>
       </c>
       <c r="P2" t="n">
         <v>7050</v>
@@ -670,13 +670,13 @@
         <v>0.02</v>
       </c>
       <c r="E3" t="n">
-        <v>386</v>
+        <v>390</v>
       </c>
       <c r="F3" t="n">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="G3" t="n">
-        <v>1604</v>
+        <v>1623</v>
       </c>
       <c r="H3" t="n">
         <v>37.72</v>
@@ -702,7 +702,7 @@
         <v>37.7</v>
       </c>
       <c r="O3" t="n">
-        <v>633732924700</v>
+        <v>634313184300</v>
       </c>
       <c r="P3" t="n">
         <v>67300</v>
@@ -718,12 +718,12 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>어닝 서프라이즈 실적 발표 및 자사주 취득, MSCI 편입 예상 등 긍정적 요인 다수 확인. 공매도 감소 기대.</t>
+          <t>삼성E&amp;A, 시장 예상 상회하는 어닝 서프라이즈 기록. 자사주 취득 공시와 MSCI 편입 예상 등 긍정적 모멘텀. 공매도 청산 기대감.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
@@ -762,13 +762,13 @@
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="F4" t="n">
         <v>32</v>
       </c>
       <c r="G4" t="n">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
@@ -854,13 +854,13 @@
         <v>-0.39</v>
       </c>
       <c r="E5" t="n">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="F5" t="n">
         <v>61</v>
       </c>
       <c r="G5" t="n">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="H5" t="n">
         <v>0.3</v>
@@ -886,7 +886,7 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="O5" t="n">
-        <v>23407692658</v>
+        <v>23412875566</v>
       </c>
       <c r="P5" t="n">
         <v>3980</v>
@@ -902,16 +902,16 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>주가 조작 의혹 제기 및 하락세 지속. 보호예수 해제 물량 부담, 단타 세력의 움직임에 대한 관망세.</t>
+          <t>보호예수 물량 해제 관련 우려와 주가조작 의혹 제기. 투자 심리 위축.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['주가 조작', '하락세', '보호예수 해제']</t>
+          <t>['보호예수 해제', '주가조작 의혹', '투자 심리']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -946,13 +946,13 @@
         <v>-0.02</v>
       </c>
       <c r="E6" t="n">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="F6" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G6" t="n">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="H6" t="n">
         <v>5.01</v>
@@ -978,7 +978,7 @@
         <v>5.03</v>
       </c>
       <c r="O6" t="n">
-        <v>29804166788</v>
+        <v>29808960608</v>
       </c>
       <c r="P6" t="n">
         <v>4980</v>
@@ -1038,13 +1038,13 @@
         <v>0.13</v>
       </c>
       <c r="E7" t="n">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="F7" t="n">
         <v>49</v>
       </c>
       <c r="G7" t="n">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="H7" t="n">
         <v>9.949999999999999</v>
@@ -1070,7 +1070,7 @@
         <v>9.82</v>
       </c>
       <c r="O7" t="n">
-        <v>43095418955</v>
+        <v>43124972975</v>
       </c>
       <c r="P7" t="n">
         <v>40350</v>
@@ -1130,13 +1130,13 @@
         <v>0.02</v>
       </c>
       <c r="E8" t="n">
-        <v>211</v>
+        <v>219</v>
       </c>
       <c r="F8" t="n">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="G8" t="n">
-        <v>840</v>
+        <v>866</v>
       </c>
       <c r="H8" t="n">
         <v>25.47</v>
@@ -1162,7 +1162,7 @@
         <v>25.45</v>
       </c>
       <c r="O8" t="n">
-        <v>22519523045</v>
+        <v>22526138495</v>
       </c>
       <c r="P8" t="n">
         <v>17950</v>
@@ -1222,13 +1222,13 @@
         <v>-0.14</v>
       </c>
       <c r="E9" t="n">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="F9" t="n">
         <v>110</v>
       </c>
       <c r="G9" t="n">
-        <v>945</v>
+        <v>957</v>
       </c>
       <c r="H9" t="n">
         <v>13.09</v>
@@ -1254,7 +1254,7 @@
         <v>13.23</v>
       </c>
       <c r="O9" t="n">
-        <v>16088234725</v>
+        <v>16091001825</v>
       </c>
       <c r="P9" t="n">
         <v>69200</v>
@@ -1314,13 +1314,13 @@
         <v>0.53</v>
       </c>
       <c r="E10" t="n">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="F10" t="n">
         <v>65</v>
       </c>
       <c r="G10" t="n">
-        <v>406</v>
+        <v>412</v>
       </c>
       <c r="H10" t="n">
         <v>5.87</v>
@@ -1346,7 +1346,7 @@
         <v>5.34</v>
       </c>
       <c r="O10" t="n">
-        <v>18981303440</v>
+        <v>18986327560</v>
       </c>
       <c r="P10" t="n">
         <v>14940</v>
@@ -1362,7 +1362,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>테슬라 실적 상회 및 스페이스X 관련 뉴스 언급. 코스피 지수 하락 속에서 상대적 선방 및 개미 털기 가능성 제기.</t>
+          <t>테슬라 실적 호조 및 스페이스X 관련 뉴스. 코스피 하락장 속에서 상대적 선방.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
@@ -1371,7 +1371,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['테슬라', '스페이스X', '개미 털기']</t>
+          <t>['테슬라 실적', '스페이스X', '주가 방어']</t>
         </is>
       </c>
       <c r="X10" t="n">
@@ -1406,13 +1406,13 @@
         <v>-0.32</v>
       </c>
       <c r="E11" t="n">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="F11" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G11" t="n">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="H11" t="n">
         <v>3.29</v>
@@ -1438,7 +1438,7 @@
         <v>3.61</v>
       </c>
       <c r="O11" t="n">
-        <v>81266757895</v>
+        <v>81284975395</v>
       </c>
       <c r="P11" t="n">
         <v>22450</v>
@@ -1501,10 +1501,10 @@
         <v>800</v>
       </c>
       <c r="F12" t="n">
-        <v>535</v>
+        <v>525</v>
       </c>
       <c r="G12" t="n">
-        <v>1686</v>
+        <v>1711</v>
       </c>
       <c r="H12" t="n">
         <v>46.14</v>
@@ -1530,7 +1530,7 @@
         <v>46.08</v>
       </c>
       <c r="O12" t="n">
-        <v>2386242649500</v>
+        <v>2388539515500</v>
       </c>
       <c r="P12" t="n">
         <v>374500</v>
@@ -1546,16 +1546,16 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>정치적 불만 표출과 함께 주가 하락에 대한 부정적 감정 표현.</t>
+          <t>정치적 이슈와 정부 정책 관련 부정적 여론 형성. 시장 전반의 약세와 투자 심리 위축.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['정치적 이슈', '시장 약세', '정부 정책']</t>
         </is>
       </c>
       <c r="X12" t="n">
@@ -1593,10 +1593,10 @@
         <v>800</v>
       </c>
       <c r="F13" t="n">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="G13" t="n">
-        <v>1978</v>
+        <v>1854</v>
       </c>
       <c r="H13" t="n">
         <v>48.79</v>
@@ -1622,7 +1622,7 @@
         <v>48.77</v>
       </c>
       <c r="O13" t="n">
-        <v>2988293509000</v>
+        <v>2988335091000</v>
       </c>
       <c r="P13" t="n">
         <v>2987000</v>
@@ -1638,16 +1638,16 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>정치적 불만과 경영진에 대한 강한 비판, 주가 하락에 대한 좌절감 표출.</t>
+          <t>정치적 이슈 및 경영진 관련 비판 여론 확산. 주가 하락에 대한 불만과 투자 심리 악화.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['주가하락', '경영진', '손실']</t>
+          <t>['정치적 이슈', '경영진 비판', '주가 하락']</t>
         </is>
       </c>
       <c r="X13" t="n">
@@ -1682,13 +1682,13 @@
         <v>0.33</v>
       </c>
       <c r="E14" t="n">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="F14" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="G14" t="n">
-        <v>626</v>
+        <v>639</v>
       </c>
       <c r="H14" t="n">
         <v>3.48</v>
@@ -1714,7 +1714,7 @@
         <v>3.15</v>
       </c>
       <c r="O14" t="n">
-        <v>121267175095</v>
+        <v>121275192435</v>
       </c>
       <c r="P14" t="n">
         <v>31500</v>
@@ -1774,13 +1774,13 @@
         <v>1.2</v>
       </c>
       <c r="E15" t="n">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="F15" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G15" t="n">
-        <v>257</v>
+        <v>266</v>
       </c>
       <c r="H15" t="n">
         <v>1.2</v>
@@ -1806,7 +1806,7 @@
         <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>84901254430</v>
+        <v>84913004830</v>
       </c>
       <c r="P15" t="n">
         <v>28800</v>
@@ -1822,16 +1822,16 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>주가 하락과 관련된 부정적 언급, 특정 종목 동반 하락 및 주포에 대한 불신 표출.</t>
+          <t>대만 반도체 파업 및 AI/반도체 섹터 관련 언급. 보호예수 해제 임박으로 인한 변동성.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['주가하락', '보호예수', '주포']</t>
+          <t>['대만 반도체', 'AI 섹터', '보호예수 해제']</t>
         </is>
       </c>
       <c r="X15" t="n">
@@ -1866,13 +1866,13 @@
         <v>2.41</v>
       </c>
       <c r="E16" t="n">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="F16" t="n">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="G16" t="n">
-        <v>547</v>
+        <v>575</v>
       </c>
       <c r="H16" t="n">
         <v>3.69</v>
@@ -1898,7 +1898,7 @@
         <v>1.28</v>
       </c>
       <c r="O16" t="n">
-        <v>66035092805</v>
+        <v>66069802405</v>
       </c>
       <c r="P16" t="n">
         <v>11690</v>
@@ -1914,16 +1914,16 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>투기예고, 급락 가능성에 대한 우려. 외국인 허매수 후 매도, 개미 물량 증가. ESS 마진율 불확실성 언급.</t>
+          <t>예상치 못한 변수 발생 및 조정 국면. 외국인 매도세와 ESS 마진율 불확실성.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['투기예고', '급락', '외국인 매도']</t>
+          <t>['예상치 못한 변수', '조정 국면', '외국인 매도']</t>
         </is>
       </c>
       <c r="X16" t="n">
